--- a/ccd-definitions/jurisdictions/scotland/data/ccd-template.xlsx
+++ b/ccd-definitions/jurisdictions/scotland/data/ccd-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tensaybulcha/Documents/GitHub/Reformed-ET/et-ccd-definitions-scotland/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rajaram/Projects/et-ccd-callbacks/ccd-definitions/jurisdictions/scotland/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC4C04A-FD68-494F-9313-B06A081DBDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D1D8D2-894D-E94E-AA1F-8BB92AFA0FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31700" yWindow="960" windowWidth="39760" windowHeight="15800" tabRatio="500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SearchParty" sheetId="36" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">CaseEventToFields!$A$3:$Q$231</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">CaseField!$A$3:$U$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CaseRoles!$A$3:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CaseTypeTab!$A$3:$P$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CaseTypeTab!$A$3:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">ComplexTypes!$A$3:$W$559</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">EventToComplexTypes!$A$3:$I$382</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Scotland Scrubbed'!$A$3:$F$646</definedName>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="395">
   <si>
     <t>Jurisdiction</t>
   </si>
@@ -1339,6 +1339,9 @@
   </si>
   <si>
     <t>TTLIncrement</t>
+  </si>
+  <si>
+    <t>This will allow you to display the tab based on access profile</t>
   </si>
 </sst>
 </file>
@@ -24815,7 +24818,9 @@
       <c r="J2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="36"/>
+      <c r="K2" s="23" t="s">
+        <v>394</v>
+      </c>
       <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:16" ht="42">
@@ -24849,7 +24854,9 @@
       <c r="J3" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="14"/>
+      <c r="K3" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
       <c r="N3" s="14"/>
@@ -25378,6 +25385,7 @@
       <c r="G99" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:K3" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <phoneticPr fontId="49" type="noConversion"/>
   <conditionalFormatting sqref="F88:F89">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
